--- a/results_hybrid/hybrid_planning_alpha_1.2.xlsx
+++ b/results_hybrid/hybrid_planning_alpha_1.2.xlsx
@@ -11,8 +11,6 @@
     <sheet name="Gamma_2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Gamma_3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Gamma_4" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Gamma_5" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Gamma_6" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -635,14 +633,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="F9" t="n">
-        <v>0.636</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="10">
@@ -659,14 +657,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8420000000000001</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="11">
@@ -683,14 +681,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P35</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.2</v>
+        <v>0.74</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>0.9259999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -707,14 +705,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P36</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1.352</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="13">
@@ -731,14 +729,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P42</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.07</v>
+        <v>0.63</v>
       </c>
       <c r="F13" t="n">
-        <v>1.304</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="14">
@@ -755,14 +753,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P43</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="F14" t="n">
-        <v>1.272</v>
+        <v>1.082</v>
       </c>
     </row>
     <row r="15">
@@ -779,14 +777,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P47</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.58</v>
+        <v>1.61</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8079999999999999</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="16">
@@ -803,14 +801,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P50</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="F16" t="n">
-        <v>0.966</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="17">
@@ -818,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -827,14 +825,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P40</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.622</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="18">
@@ -846,19 +844,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="F18" t="n">
-        <v>0.706</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="19">
@@ -870,19 +868,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.74</v>
+        <v>0.34</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9259999999999999</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +892,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="F20" t="n">
-        <v>1.21</v>
+        <v>0.6060000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -918,19 +916,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.63</v>
+        <v>0.91</v>
       </c>
       <c r="F21" t="n">
-        <v>0.798</v>
+        <v>1.168</v>
       </c>
     </row>
     <row r="22">
@@ -942,19 +940,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="F22" t="n">
-        <v>1.082</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="23">
@@ -966,19 +964,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.61</v>
+        <v>0.57</v>
       </c>
       <c r="F23" t="n">
-        <v>1.748</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="24">
@@ -990,19 +988,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P34</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="F24" t="n">
-        <v>0.994</v>
+        <v>0.716</v>
       </c>
     </row>
     <row r="25">
@@ -1014,19 +1012,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P40</t>
+          <t>P37</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="F25" t="n">
-        <v>0.752</v>
+        <v>0.8799999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1034,23 +1032,23 @@
         <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P48</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.13</v>
+        <v>0.39</v>
       </c>
       <c r="F26" t="n">
-        <v>1.364</v>
+        <v>0.5940000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1058,23 +1056,23 @@
         <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P54</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>2.914</v>
+        <v>0.7220000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1091,14 +1089,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="F28" t="n">
-        <v>1.236</v>
+        <v>1.364</v>
       </c>
     </row>
     <row r="29">
@@ -1115,14 +1113,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P44</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.75</v>
+        <v>2.62</v>
       </c>
       <c r="F29" t="n">
-        <v>0.918</v>
+        <v>2.914</v>
       </c>
     </row>
     <row r="30">
@@ -1139,14 +1137,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P45</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.88</v>
+        <v>1.05</v>
       </c>
       <c r="F30" t="n">
-        <v>2.048</v>
+        <v>1.236</v>
       </c>
     </row>
     <row r="31">
@@ -1154,23 +1152,23 @@
         <v>1</v>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P44</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="F31" t="n">
-        <v>0.704</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="32">
@@ -1178,23 +1176,23 @@
         <v>1</v>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P45</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.34</v>
+        <v>1.88</v>
       </c>
       <c r="F32" t="n">
-        <v>0.664</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="33">
@@ -1206,19 +1204,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6060000000000001</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="34">
@@ -1230,19 +1228,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.91</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>1.168</v>
+        <v>0.8420000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1254,19 +1252,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>P23</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.53</v>
+        <v>1.2</v>
       </c>
       <c r="F35" t="n">
-        <v>0.794</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="36">
@@ -1278,19 +1276,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P29</t>
+          <t>P36</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="F36" t="n">
-        <v>0.774</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="37">
@@ -1302,19 +1300,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>P34</t>
+          <t>P42</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.47</v>
+        <v>1.07</v>
       </c>
       <c r="F37" t="n">
-        <v>0.716</v>
+        <v>1.304</v>
       </c>
     </row>
     <row r="38">
@@ -1326,19 +1324,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P37</t>
+          <t>P43</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.58</v>
+        <v>1.02</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8799999999999999</v>
+        <v>1.272</v>
       </c>
     </row>
     <row r="39">
@@ -1350,19 +1348,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>P48</t>
+          <t>P47</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.39</v>
+        <v>0.58</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5940000000000001</v>
+        <v>0.8079999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1374,19 +1372,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P54</t>
+          <t>P50</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7220000000000001</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="41">
@@ -1523,14 +1521,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.34</v>
+        <v>0.61</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6100000000000001</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="47">
@@ -1547,14 +1545,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P46</t>
+          <t>P33</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6699999999999999</v>
+        <v>0.6100000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1571,14 +1569,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P49</t>
+          <t>P39</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.91</v>
+        <v>0.3</v>
       </c>
       <c r="F48" t="n">
-        <v>1.234</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="49">
@@ -1595,14 +1593,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>P51</t>
+          <t>P46</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.6699999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -1610,7 +1608,7 @@
         <v>1</v>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1619,14 +1617,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P53</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.26</v>
+        <v>0.51</v>
       </c>
       <c r="F50" t="n">
-        <v>0.398</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="51">
@@ -1643,14 +1641,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="F51" t="n">
-        <v>0.88</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="52">
@@ -1667,14 +1665,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.64</v>
+        <v>0.49</v>
       </c>
       <c r="F52" t="n">
-        <v>0.994</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="53">
@@ -1691,14 +1689,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="F53" t="n">
-        <v>0.754</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="54">
@@ -1715,14 +1713,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P39</t>
+          <t>P41</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.3</v>
+        <v>1.47</v>
       </c>
       <c r="F54" t="n">
-        <v>0.708</v>
+        <v>1.842</v>
       </c>
     </row>
     <row r="55">
@@ -1739,14 +1737,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>P41</t>
+          <t>P49</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.47</v>
+        <v>0.91</v>
       </c>
       <c r="F55" t="n">
-        <v>1.842</v>
+        <v>1.234</v>
       </c>
     </row>
     <row r="56">
@@ -1763,14 +1761,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P52</t>
+          <t>P51</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.04</v>
+        <v>0.2</v>
       </c>
       <c r="F56" t="n">
-        <v>1.232</v>
+        <v>0.5720000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -1787,14 +1785,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>P53</t>
+          <t>P52</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.51</v>
+        <v>1.04</v>
       </c>
       <c r="F57" t="n">
-        <v>0.858</v>
+        <v>1.232</v>
       </c>
     </row>
   </sheetData>
@@ -1852,19 +1850,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.13</v>
+        <v>0.46</v>
       </c>
       <c r="F2" t="n">
-        <v>1.364</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="3">
@@ -1876,19 +1874,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.62</v>
+        <v>0.52</v>
       </c>
       <c r="F3" t="n">
-        <v>2.914</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="4">
@@ -1900,19 +1898,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.05</v>
+        <v>0.74</v>
       </c>
       <c r="F4" t="n">
-        <v>1.236</v>
+        <v>0.9259999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1924,19 +1922,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P44</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.918</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="6">
@@ -1948,19 +1946,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P45</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.88</v>
+        <v>0.63</v>
       </c>
       <c r="F6" t="n">
-        <v>2.048</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="7">
@@ -1968,7 +1966,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1977,14 +1975,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9259999999999999</v>
+        <v>1.082</v>
       </c>
     </row>
     <row r="8">
@@ -1992,7 +1990,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2001,14 +1999,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.36</v>
+        <v>1.61</v>
       </c>
       <c r="F8" t="n">
-        <v>0.636</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="9">
@@ -2016,7 +2014,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2025,14 +2023,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8420000000000001</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="10">
@@ -2040,7 +2038,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2049,14 +2047,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P35</t>
+          <t>P40</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="11">
@@ -2073,14 +2071,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P36</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.13</v>
+        <v>0.36</v>
       </c>
       <c r="F11" t="n">
-        <v>1.352</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="12">
@@ -2097,14 +2095,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P42</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.07</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.304</v>
+        <v>0.8420000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2121,14 +2119,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P43</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1.272</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14">
@@ -2145,14 +2143,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P47</t>
+          <t>P36</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.58</v>
+        <v>1.13</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8079999999999999</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="15">
@@ -2169,14 +2167,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P50</t>
+          <t>P42</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.75</v>
+        <v>1.07</v>
       </c>
       <c r="F15" t="n">
-        <v>0.966</v>
+        <v>1.304</v>
       </c>
     </row>
     <row r="16">
@@ -2184,23 +2182,23 @@
         <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P43</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="F16" t="n">
-        <v>1.964</v>
+        <v>1.272</v>
       </c>
     </row>
     <row r="17">
@@ -2208,23 +2206,23 @@
         <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P47</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.44</v>
+        <v>0.58</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8</v>
+        <v>0.8079999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -2232,23 +2230,23 @@
         <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P50</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="F18" t="n">
-        <v>0.702</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="19">
@@ -2260,19 +2258,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="F19" t="n">
-        <v>1.502</v>
+        <v>1.364</v>
       </c>
     </row>
     <row r="20">
@@ -2284,19 +2282,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P27</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.7</v>
+        <v>2.62</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2.914</v>
       </c>
     </row>
     <row r="21">
@@ -2308,19 +2306,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P38</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="F21" t="n">
-        <v>1.404</v>
+        <v>1.236</v>
       </c>
     </row>
     <row r="22">
@@ -2332,19 +2330,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P55</t>
+          <t>P44</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="F22" t="n">
-        <v>0.72</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="23">
@@ -2352,23 +2350,23 @@
         <v>2</v>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P45</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.46</v>
+        <v>1.88</v>
       </c>
       <c r="F23" t="n">
-        <v>0.622</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="24">
@@ -2380,19 +2378,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.52</v>
+        <v>1.76</v>
       </c>
       <c r="F24" t="n">
-        <v>0.706</v>
+        <v>1.964</v>
       </c>
     </row>
     <row r="25">
@@ -2404,19 +2402,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.44</v>
       </c>
       <c r="F25" t="n">
-        <v>1.21</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
@@ -2428,19 +2426,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="F26" t="n">
-        <v>0.798</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="27">
@@ -2452,19 +2450,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.89</v>
+        <v>1.31</v>
       </c>
       <c r="F27" t="n">
-        <v>1.082</v>
+        <v>1.502</v>
       </c>
     </row>
     <row r="28">
@@ -2476,19 +2474,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.61</v>
+        <v>0.7</v>
       </c>
       <c r="F28" t="n">
-        <v>1.748</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2500,19 +2498,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P38</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="F29" t="n">
-        <v>0.994</v>
+        <v>1.404</v>
       </c>
     </row>
     <row r="30">
@@ -2524,19 +2522,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P40</t>
+          <t>P55</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="F30" t="n">
-        <v>0.752</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="31">
@@ -2865,14 +2863,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P33</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.51</v>
+        <v>0.34</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6100000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -2889,14 +2887,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P39</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6639999999999999</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="46">
@@ -2913,14 +2911,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P41</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.34</v>
+        <v>1.47</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6100000000000001</v>
+        <v>1.842</v>
       </c>
     </row>
     <row r="47">
@@ -2937,14 +2935,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P39</t>
+          <t>P51</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F47" t="n">
-        <v>0.708</v>
+        <v>0.5720000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2961,14 +2959,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P41</t>
+          <t>P53</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.47</v>
+        <v>0.51</v>
       </c>
       <c r="F48" t="n">
-        <v>1.842</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="49">
@@ -3033,14 +3031,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.38</v>
+        <v>0.51</v>
       </c>
       <c r="F51" t="n">
-        <v>0.608</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3057,14 +3055,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P31</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.61</v>
+        <v>0.38</v>
       </c>
       <c r="F52" t="n">
-        <v>0.754</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="53">
@@ -3081,14 +3079,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>P46</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.31</v>
+        <v>0.49</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6699999999999999</v>
+        <v>0.6639999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -3105,14 +3103,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P49</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.91</v>
+        <v>0.61</v>
       </c>
       <c r="F54" t="n">
-        <v>1.234</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="55">
@@ -3129,14 +3127,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>P51</t>
+          <t>P46</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.6699999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -3153,14 +3151,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P52</t>
+          <t>P49</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="F56" t="n">
-        <v>1.232</v>
+        <v>1.234</v>
       </c>
     </row>
     <row r="57">
@@ -3177,14 +3175,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>P53</t>
+          <t>P52</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.51</v>
+        <v>1.04</v>
       </c>
       <c r="F57" t="n">
-        <v>0.858</v>
+        <v>1.232</v>
       </c>
     </row>
   </sheetData>
@@ -3242,19 +3240,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="F2" t="n">
-        <v>0.622</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="3">
@@ -3266,19 +3264,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.52</v>
+        <v>0.34</v>
       </c>
       <c r="F3" t="n">
-        <v>0.706</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="4">
@@ -3290,19 +3288,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.74</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9259999999999999</v>
+        <v>0.6060000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3314,19 +3312,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="F5" t="n">
-        <v>1.21</v>
+        <v>1.168</v>
       </c>
     </row>
     <row r="6">
@@ -3338,19 +3336,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.63</v>
+        <v>0.53</v>
       </c>
       <c r="F6" t="n">
-        <v>0.798</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="7">
@@ -3362,19 +3360,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="F7" t="n">
-        <v>1.082</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="8">
@@ -3386,19 +3384,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>P34</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.61</v>
+        <v>0.47</v>
       </c>
       <c r="F8" t="n">
-        <v>1.748</v>
+        <v>0.716</v>
       </c>
     </row>
     <row r="9">
@@ -3410,19 +3408,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P37</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="F9" t="n">
-        <v>0.994</v>
+        <v>0.8799999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -3434,19 +3432,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P40</t>
+          <t>P48</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752</v>
+        <v>0.5940000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -3454,23 +3452,23 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P54</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.364</v>
+        <v>0.7220000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3482,19 +3480,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.62</v>
+        <v>0.36</v>
       </c>
       <c r="F12" t="n">
-        <v>2.914</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="13">
@@ -3506,19 +3504,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.236</v>
+        <v>0.8420000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -3530,19 +3528,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P44</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.918</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15">
@@ -3554,19 +3552,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P45</t>
+          <t>P36</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.88</v>
+        <v>1.13</v>
       </c>
       <c r="F15" t="n">
-        <v>2.048</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="16">
@@ -3574,23 +3572,23 @@
         <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P42</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.44</v>
+        <v>1.07</v>
       </c>
       <c r="F16" t="n">
-        <v>0.704</v>
+        <v>1.304</v>
       </c>
     </row>
     <row r="17">
@@ -3598,23 +3596,23 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P43</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.34</v>
+        <v>1.02</v>
       </c>
       <c r="F17" t="n">
-        <v>0.664</v>
+        <v>1.272</v>
       </c>
     </row>
     <row r="18">
@@ -3622,23 +3620,23 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P47</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.33</v>
+        <v>0.58</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6060000000000001</v>
+        <v>0.8079999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -3646,23 +3644,23 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P50</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
       <c r="F19" t="n">
-        <v>1.168</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="20">
@@ -3674,19 +3672,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P23</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="F20" t="n">
-        <v>0.794</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="21">
@@ -3698,19 +3696,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P29</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="F21" t="n">
-        <v>0.774</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="22">
@@ -3722,19 +3720,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P34</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="F22" t="n">
-        <v>0.716</v>
+        <v>0.9259999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3746,19 +3744,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P37</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8799999999999999</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="24">
@@ -3770,19 +3768,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P48</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5940000000000001</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="25">
@@ -3794,19 +3792,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P54</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7220000000000001</v>
+        <v>1.082</v>
       </c>
     </row>
     <row r="26">
@@ -3814,23 +3812,23 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="F26" t="n">
-        <v>1.964</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="27">
@@ -3838,23 +3836,23 @@
         <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.44</v>
+        <v>0.82</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="28">
@@ -3862,23 +3860,23 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P40</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.702</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="29">
@@ -3890,19 +3888,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="F29" t="n">
-        <v>1.502</v>
+        <v>1.364</v>
       </c>
     </row>
     <row r="30">
@@ -3914,19 +3912,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P27</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.7</v>
+        <v>2.62</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>2.914</v>
       </c>
     </row>
     <row r="31">
@@ -3938,19 +3936,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P38</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="F31" t="n">
-        <v>1.404</v>
+        <v>1.236</v>
       </c>
     </row>
     <row r="32">
@@ -3962,19 +3960,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P55</t>
+          <t>P44</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="F32" t="n">
-        <v>0.72</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="33">
@@ -3982,23 +3980,23 @@
         <v>3</v>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P45</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.36</v>
+        <v>1.88</v>
       </c>
       <c r="F33" t="n">
-        <v>0.636</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="34">
@@ -4010,19 +4008,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8420000000000001</v>
+        <v>1.964</v>
       </c>
     </row>
     <row r="35">
@@ -4034,19 +4032,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>P35</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>0.44</v>
       </c>
       <c r="F35" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="36">
@@ -4058,19 +4056,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P36</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="F36" t="n">
-        <v>1.352</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="37">
@@ -4082,19 +4080,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>P42</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="F37" t="n">
-        <v>1.304</v>
+        <v>1.502</v>
       </c>
     </row>
     <row r="38">
@@ -4106,19 +4104,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P43</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.02</v>
+        <v>0.7</v>
       </c>
       <c r="F38" t="n">
-        <v>1.272</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -4130,19 +4128,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>P47</t>
+          <t>P38</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.58</v>
+        <v>0.99</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8079999999999999</v>
+        <v>1.404</v>
       </c>
     </row>
     <row r="40">
@@ -4154,19 +4152,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P50</t>
+          <t>P55</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="F40" t="n">
-        <v>0.966</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="41">
@@ -4207,14 +4205,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.64</v>
+        <v>0.49</v>
       </c>
       <c r="F42" t="n">
-        <v>0.994</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="43">
@@ -4231,14 +4229,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="44">
@@ -4255,14 +4253,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P39</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="F44" t="n">
-        <v>0.708</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -4279,14 +4277,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>P41</t>
+          <t>P39</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.47</v>
+        <v>0.3</v>
       </c>
       <c r="F45" t="n">
-        <v>1.842</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="46">
@@ -4327,14 +4325,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P51</t>
+          <t>P49</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5720000000000001</v>
+        <v>1.234</v>
       </c>
     </row>
     <row r="48">
@@ -4351,14 +4349,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P53</t>
+          <t>P51</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.51</v>
+        <v>0.2</v>
       </c>
       <c r="F48" t="n">
-        <v>0.858</v>
+        <v>0.5720000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4366,7 +4364,7 @@
         <v>3</v>
       </c>
       <c r="B49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -4375,14 +4373,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P53</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="F49" t="n">
-        <v>0.954</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="50">
@@ -4399,14 +4397,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>0.398</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="51">
@@ -4423,14 +4421,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="F51" t="n">
-        <v>0.88</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="52">
@@ -4543,14 +4541,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P49</t>
+          <t>P41</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.91</v>
+        <v>1.47</v>
       </c>
       <c r="F56" t="n">
-        <v>1.234</v>
+        <v>1.842</v>
       </c>
     </row>
     <row r="57">
@@ -4632,19 +4630,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.46</v>
+        <v>1.13</v>
       </c>
       <c r="F2" t="n">
-        <v>0.622</v>
+        <v>1.364</v>
       </c>
     </row>
     <row r="3">
@@ -4656,19 +4654,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.52</v>
+        <v>2.62</v>
       </c>
       <c r="F3" t="n">
-        <v>0.706</v>
+        <v>2.914</v>
       </c>
     </row>
     <row r="4">
@@ -4680,19 +4678,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.74</v>
+        <v>1.05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9259999999999999</v>
+        <v>1.236</v>
       </c>
     </row>
     <row r="5">
@@ -4704,19 +4702,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P44</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F5" t="n">
-        <v>1.21</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="6">
@@ -4728,19 +4726,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>VASCULAR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P45</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.63</v>
+        <v>1.88</v>
       </c>
       <c r="F6" t="n">
-        <v>0.798</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="7">
@@ -4748,7 +4746,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -4757,14 +4755,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="F7" t="n">
-        <v>1.082</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="8">
@@ -4772,7 +4770,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -4781,14 +4779,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.61</v>
+        <v>0.52</v>
       </c>
       <c r="F8" t="n">
-        <v>1.748</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="9">
@@ -4796,7 +4794,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -4805,14 +4803,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="F9" t="n">
-        <v>0.994</v>
+        <v>0.9259999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -4820,7 +4818,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -4829,14 +4827,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P40</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="11">
@@ -4848,19 +4846,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.76</v>
+        <v>0.63</v>
       </c>
       <c r="F11" t="n">
-        <v>1.964</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="12">
@@ -4872,19 +4870,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8</v>
+        <v>1.082</v>
       </c>
     </row>
     <row r="13">
@@ -4896,19 +4894,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.45</v>
+        <v>1.61</v>
       </c>
       <c r="F13" t="n">
-        <v>0.702</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="14">
@@ -4920,19 +4918,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="F14" t="n">
-        <v>1.502</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="15">
@@ -4944,19 +4942,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>P27</t>
+          <t>P40</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="16">
@@ -4964,7 +4962,7 @@
         <v>4</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4973,14 +4971,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P38</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.99</v>
+        <v>1.76</v>
       </c>
       <c r="F16" t="n">
-        <v>1.404</v>
+        <v>1.964</v>
       </c>
     </row>
     <row r="17">
@@ -4988,7 +4986,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4997,14 +4995,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>P55</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="F17" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18">
@@ -5016,19 +5014,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="F18" t="n">
-        <v>1.364</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="19">
@@ -5040,19 +5038,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.62</v>
+        <v>1.31</v>
       </c>
       <c r="F19" t="n">
-        <v>2.914</v>
+        <v>1.502</v>
       </c>
     </row>
     <row r="20">
@@ -5064,19 +5062,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="F20" t="n">
-        <v>1.236</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -5088,19 +5086,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P44</t>
+          <t>P38</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="F21" t="n">
-        <v>0.918</v>
+        <v>1.404</v>
       </c>
     </row>
     <row r="22">
@@ -5112,19 +5110,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VASCULAR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P45</t>
+          <t>P55</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.88</v>
+        <v>0.45</v>
       </c>
       <c r="F22" t="n">
-        <v>2.048</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="23">
@@ -5136,19 +5134,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.44</v>
+        <v>0.36</v>
       </c>
       <c r="F23" t="n">
-        <v>0.704</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="24">
@@ -5160,19 +5158,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.34</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.664</v>
+        <v>0.8420000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -5184,19 +5182,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.33</v>
+        <v>1.2</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6060000000000001</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="26">
@@ -5208,19 +5206,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P36</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.91</v>
+        <v>1.13</v>
       </c>
       <c r="F26" t="n">
-        <v>1.168</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="27">
@@ -5232,19 +5230,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P23</t>
+          <t>P42</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.53</v>
+        <v>1.07</v>
       </c>
       <c r="F27" t="n">
-        <v>0.794</v>
+        <v>1.304</v>
       </c>
     </row>
     <row r="28">
@@ -5256,19 +5254,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P29</t>
+          <t>P43</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.57</v>
+        <v>1.02</v>
       </c>
       <c r="F28" t="n">
-        <v>0.774</v>
+        <v>1.272</v>
       </c>
     </row>
     <row r="29">
@@ -5280,19 +5278,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P34</t>
+          <t>P47</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="F29" t="n">
-        <v>0.716</v>
+        <v>0.8079999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -5304,19 +5302,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OBGYN</t>
+          <t>ORTHO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P37</t>
+          <t>P50</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8799999999999999</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="31">
@@ -5324,7 +5322,7 @@
         <v>4</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -5333,14 +5331,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P48</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5940000000000001</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="32">
@@ -5348,7 +5346,7 @@
         <v>4</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5357,14 +5355,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P54</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7220000000000001</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="33">
@@ -5376,19 +5374,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F33" t="n">
-        <v>0.636</v>
+        <v>0.6060000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -5400,19 +5398,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8420000000000001</v>
+        <v>1.168</v>
       </c>
     </row>
     <row r="35">
@@ -5424,19 +5422,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>P35</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>0.53</v>
       </c>
       <c r="F35" t="n">
-        <v>1.5</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="36">
@@ -5448,19 +5446,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P36</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="F36" t="n">
-        <v>1.352</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="37">
@@ -5472,19 +5470,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>P42</t>
+          <t>P34</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.07</v>
+        <v>0.47</v>
       </c>
       <c r="F37" t="n">
-        <v>1.304</v>
+        <v>0.716</v>
       </c>
     </row>
     <row r="38">
@@ -5496,19 +5494,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P43</t>
+          <t>P37</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="F38" t="n">
-        <v>1.272</v>
+        <v>0.8799999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -5520,19 +5518,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>P47</t>
+          <t>P48</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.58</v>
+        <v>0.39</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8079999999999999</v>
+        <v>0.5940000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -5544,19 +5542,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ORTHO</t>
+          <t>OBGYN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P50</t>
+          <t>P54</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.966</v>
+        <v>0.7220000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -5573,14 +5571,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="F41" t="n">
-        <v>0.804</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="42">
@@ -5597,14 +5595,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="F42" t="n">
-        <v>0.88</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="43">
@@ -5621,14 +5619,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.64</v>
+        <v>0.49</v>
       </c>
       <c r="F43" t="n">
-        <v>0.994</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="44">
@@ -5645,14 +5643,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P39</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="F44" t="n">
-        <v>0.708</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="45">
@@ -5669,14 +5667,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>P41</t>
+          <t>P39</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.47</v>
+        <v>0.3</v>
       </c>
       <c r="F45" t="n">
-        <v>1.842</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="46">
@@ -5693,14 +5691,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P46</t>
+          <t>P41</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.31</v>
+        <v>1.47</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6699999999999999</v>
+        <v>1.842</v>
       </c>
     </row>
     <row r="47">
@@ -5717,14 +5715,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>P51</t>
+          <t>P46</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.6699999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -5741,14 +5739,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P53</t>
+          <t>P51</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.51</v>
+        <v>0.2</v>
       </c>
       <c r="F48" t="n">
-        <v>0.858</v>
+        <v>0.5720000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -5756,7 +5754,7 @@
         <v>4</v>
       </c>
       <c r="B49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5765,14 +5763,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P53</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="F49" t="n">
-        <v>0.954</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="50">
@@ -5789,14 +5787,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>0.398</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="51">
@@ -5946,2786 +5944,6 @@
     <row r="57">
       <c r="A57" t="n">
         <v>4</v>
-      </c>
-      <c r="B57" t="n">
-        <v>7</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>P52</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1.232</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F57"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Spec</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Hybrid_Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.622</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.706</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9259999999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.798</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>P25</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.082</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>P26</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.748</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>P28</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.994</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>P40</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.752</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>VASCULAR</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.364</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>VASCULAR</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>P24</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.914</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>VASCULAR</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>P30</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.236</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>VASCULAR</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>P44</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.918</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>VASCULAR</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>P45</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.048</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>P12</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.636</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>P32</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.8420000000000001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>P35</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>P36</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.352</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>P42</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.304</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>P43</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1.272</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" t="n">
-        <v>3</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>P47</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.8079999999999999</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>P50</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.966</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.704</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.664</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.6060000000000001</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" t="n">
-        <v>4</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1.168</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B28" t="n">
-        <v>4</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>P23</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.794</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>P29</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.774</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" t="n">
-        <v>4</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>P34</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.716</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>5</v>
-      </c>
-      <c r="B31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>P37</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.8799999999999999</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>5</v>
-      </c>
-      <c r="B32" t="n">
-        <v>4</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>P48</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.5940000000000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>P54</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.7220000000000001</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1.964</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B35" t="n">
-        <v>5</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>5</v>
-      </c>
-      <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.702</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>5</v>
-      </c>
-      <c r="B37" t="n">
-        <v>5</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1.502</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>5</v>
-      </c>
-      <c r="B38" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>P27</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>5</v>
-      </c>
-      <c r="B39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>P38</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.404</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>5</v>
-      </c>
-      <c r="B40" t="n">
-        <v>5</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>P55</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>5</v>
-      </c>
-      <c r="B41" t="n">
-        <v>6</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.804</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>5</v>
-      </c>
-      <c r="B42" t="n">
-        <v>6</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>5</v>
-      </c>
-      <c r="B43" t="n">
-        <v>6</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.994</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>5</v>
-      </c>
-      <c r="B44" t="n">
-        <v>6</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>5</v>
-      </c>
-      <c r="B45" t="n">
-        <v>6</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.608</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>5</v>
-      </c>
-      <c r="B46" t="n">
-        <v>6</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>P33</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.6100000000000001</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>5</v>
-      </c>
-      <c r="B47" t="n">
-        <v>6</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>P39</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.708</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>5</v>
-      </c>
-      <c r="B48" t="n">
-        <v>6</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>P46</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.6699999999999999</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>5</v>
-      </c>
-      <c r="B49" t="n">
-        <v>6</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>P51</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.5720000000000001</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>5</v>
-      </c>
-      <c r="B50" t="n">
-        <v>6</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>P53</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.858</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>5</v>
-      </c>
-      <c r="B51" t="n">
-        <v>7</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.954</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>5</v>
-      </c>
-      <c r="B52" t="n">
-        <v>7</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.398</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>5</v>
-      </c>
-      <c r="B53" t="n">
-        <v>7</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.6639999999999999</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>5</v>
-      </c>
-      <c r="B54" t="n">
-        <v>7</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>P31</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.754</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>5</v>
-      </c>
-      <c r="B55" t="n">
-        <v>7</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>P41</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1.842</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>5</v>
-      </c>
-      <c r="B56" t="n">
-        <v>7</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>P49</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1.234</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>5</v>
-      </c>
-      <c r="B57" t="n">
-        <v>7</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>P52</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1.232</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F57"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Spec</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Hybrid_Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>P12</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.636</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>P32</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.8420000000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>P35</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P36</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.352</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P42</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.304</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>P43</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.272</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>P47</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.8079999999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>P50</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.966</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.704</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.664</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.6060000000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.168</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>P23</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.794</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>P29</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.774</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>P34</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.716</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>P37</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.8799999999999999</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>P48</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.5940000000000001</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>OBGYN</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>P54</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.7220000000000001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>VASCULAR</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>P9</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.364</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>6</v>
-      </c>
-      <c r="B21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>VASCULAR</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>P24</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.914</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B22" t="n">
-        <v>3</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>VASCULAR</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>P30</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.236</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B23" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>VASCULAR</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>P44</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.918</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>6</v>
-      </c>
-      <c r="B24" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>VASCULAR</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>P45</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2.048</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B25" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1.964</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>6</v>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>6</v>
-      </c>
-      <c r="B27" t="n">
-        <v>4</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.702</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B28" t="n">
-        <v>4</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.502</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>6</v>
-      </c>
-      <c r="B29" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>P27</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>6</v>
-      </c>
-      <c r="B30" t="n">
-        <v>4</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>P38</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.404</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>6</v>
-      </c>
-      <c r="B31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>P55</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>6</v>
-      </c>
-      <c r="B32" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.622</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.706</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.9259999999999999</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>6</v>
-      </c>
-      <c r="B35" t="n">
-        <v>5</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.798</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" t="n">
-        <v>5</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>P25</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1.082</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>6</v>
-      </c>
-      <c r="B38" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>P26</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.748</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>6</v>
-      </c>
-      <c r="B39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>P28</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.994</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>6</v>
-      </c>
-      <c r="B40" t="n">
-        <v>5</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>ORTHO</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>P40</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.752</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B41" t="n">
-        <v>6</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.804</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>6</v>
-      </c>
-      <c r="B42" t="n">
-        <v>6</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>6</v>
-      </c>
-      <c r="B43" t="n">
-        <v>6</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.994</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>6</v>
-      </c>
-      <c r="B44" t="n">
-        <v>6</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>6</v>
-      </c>
-      <c r="B45" t="n">
-        <v>6</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.608</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>6</v>
-      </c>
-      <c r="B46" t="n">
-        <v>6</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>P33</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.6100000000000001</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>6</v>
-      </c>
-      <c r="B47" t="n">
-        <v>6</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>P39</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.708</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>6</v>
-      </c>
-      <c r="B48" t="n">
-        <v>6</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>P46</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.6699999999999999</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>6</v>
-      </c>
-      <c r="B49" t="n">
-        <v>6</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>P51</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.5720000000000001</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>6</v>
-      </c>
-      <c r="B50" t="n">
-        <v>6</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>P53</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.858</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>6</v>
-      </c>
-      <c r="B51" t="n">
-        <v>7</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.954</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>6</v>
-      </c>
-      <c r="B52" t="n">
-        <v>7</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>P8</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.398</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>6</v>
-      </c>
-      <c r="B53" t="n">
-        <v>7</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.6639999999999999</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>6</v>
-      </c>
-      <c r="B54" t="n">
-        <v>7</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>P31</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.754</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>6</v>
-      </c>
-      <c r="B55" t="n">
-        <v>7</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>P41</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1.842</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>6</v>
-      </c>
-      <c r="B56" t="n">
-        <v>7</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ENT</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>P49</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1.234</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>6</v>
       </c>
       <c r="B57" t="n">
         <v>7</v>
